--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484363_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484363_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.223</v>
+        <v>3.6501</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4666</v>
+        <v>3.1115</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7565</v>
+        <v>0.5386</v>
       </c>
       <c r="G2" t="n">
         <v>-0.3141</v>
@@ -610,13 +610,13 @@
         <v>2.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7009</v>
+        <v>0.1279</v>
       </c>
       <c r="T2" t="n">
-        <v>1.728</v>
+        <v>0.3729</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0271</v>
+        <v>-0.245</v>
       </c>
       <c r="V2" t="n">
         <v>1.8828</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.228</v>
+        <v>3.5941</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1541</v>
+        <v>2.5474</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0739</v>
+        <v>1.0467</v>
       </c>
       <c r="G3" t="n">
         <v>0.4567</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5211</v>
+        <v>-0.1128</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9245</v>
+        <v>0.3179</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4034</v>
+        <v>-0.4307</v>
       </c>
       <c r="V3" t="n">
         <v>1.8828</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9131</v>
+        <v>3.2435</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3505</v>
+        <v>4.2968</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5626</v>
+        <v>-1.0533</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7873</v>
+        <v>1.1109</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9225</v>
+        <v>-0.9933</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1352</v>
+        <v>2.1042</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2717</v>
+        <v>2.8526</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2717</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4844</v>
+        <v>-1.7417</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3492</v>
+        <v>-1.8759</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1352</v>
+        <v>0.1342</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3993</v>
+        <v>-1.0627</v>
       </c>
       <c r="T4" t="n">
-        <v>0.743</v>
+        <v>-0.2935</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6564</v>
+        <v>-0.7692</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6642</v>
+        <v>1.8279</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6642</v>
+        <v>2.7145</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4654</v>
+        <v>2.707</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6529</v>
+        <v>3.9762</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1875</v>
+        <v>-1.2692</v>
       </c>
       <c r="G5" t="n">
         <v>3.9455</v>
@@ -844,13 +844,13 @@
         <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9377</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7784</v>
+        <v>-0.4552</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1592</v>
+        <v>-0.2409</v>
       </c>
       <c r="V5" t="n">
         <v>-2.1052</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4106</v>
+        <v>2.6202</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8724</v>
+        <v>0.8027</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4618</v>
+        <v>1.8175</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1109</v>
+        <v>1.1505</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9933</v>
+        <v>2.2692</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1042</v>
+        <v>-1.1186</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8526</v>
+        <v>1.3151</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8826000000000001</v>
+        <v>2.0286</v>
       </c>
       <c r="L6" t="n">
-        <v>1.97</v>
+        <v>-0.7136</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7417</v>
+        <v>-0.1645</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8759</v>
+        <v>0.2405</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1342</v>
+        <v>-0.4051</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8956</v>
+        <v>-0.0344</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7179</v>
+        <v>-0.4222</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1777</v>
+        <v>0.3878</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8279</v>
+        <v>0.3321</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7145</v>
+        <v>0.8865</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8865</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1104</v>
+        <v>2.2117</v>
       </c>
       <c r="E7" t="n">
-        <v>0.075</v>
+        <v>2.4758</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0354</v>
+        <v>-0.264</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1505</v>
+        <v>0.6512</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2692</v>
+        <v>-0.0097</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1186</v>
+        <v>0.6609</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3151</v>
+        <v>1.7447</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0286</v>
+        <v>0.4093</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7136</v>
+        <v>1.3354</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1645</v>
+        <v>-1.0935</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2405</v>
+        <v>-0.419</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4051</v>
+        <v>-0.6745</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5443</v>
+        <v>-0.4161</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1499</v>
+        <v>0.1218</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6056</v>
+        <v>-0.5379</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3321</v>
+        <v>0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8865</v>
+        <v>0.6093</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8267</v>
+        <v>2.0207</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1724</v>
+        <v>1.7032</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3457</v>
+        <v>0.3175</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6512</v>
+        <v>1.7873</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0097</v>
+        <v>1.9225</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6609</v>
+        <v>-0.1352</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7447</v>
+        <v>2.2717</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4093</v>
+        <v>2.2717</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3354</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0935</v>
+        <v>-0.4844</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.419</v>
+        <v>-0.3492</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6745</v>
+        <v>-0.1352</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8012</v>
+        <v>0.5069</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1816</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6196</v>
+        <v>0.4112</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6093</v>
+        <v>-0.6642</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6093</v>
+        <v>-0.6642</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.757</v>
+        <v>1.3309</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9638</v>
+        <v>1.4287</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2067</v>
+        <v>-0.0978</v>
       </c>
       <c r="G9" t="n">
         <v>2.5263</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7693</v>
+        <v>-0.1953</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6052</v>
+        <v>-0.1402</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.164</v>
+        <v>-0.0551</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6093</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5131</v>
+        <v>-3.1008</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.548</v>
+        <v>-1.2447</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9651</v>
+        <v>-1.8561</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9372</v>
@@ -1312,13 +1312,13 @@
         <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2205</v>
+        <v>-0.8082</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.4835</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4337</v>
+        <v>-0.3247</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5507</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9582</v>
+        <v>-4.2093</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9016</v>
+        <v>-5.2344</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9434</v>
+        <v>1.0251</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8659</v>
@@ -1390,13 +1390,13 @@
         <v>2.7348</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0571</v>
+        <v>-0.3081</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2105</v>
+        <v>-0.5432</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1534</v>
+        <v>0.2351</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8865</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.0572</v>
+        <v>14.6624</v>
       </c>
       <c r="E13" t="n">
-        <v>13.2581</v>
+        <v>13.8632</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7993000000000001</v>
+        <v>0.7992999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>9.441399999999998</v>
@@ -1438,7 +1438,7 @@
         <v>4.7187</v>
       </c>
       <c r="I13" t="n">
-        <v>4.722799999999999</v>
+        <v>4.7228</v>
       </c>
       <c r="J13" t="n">
         <v>20.1984</v>
@@ -1468,13 +1468,13 @@
         <v>18.5576</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.604399999999999</v>
+        <v>-2.9989</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.0348</v>
+        <v>-1.4295</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5693</v>
+        <v>-1.5694</v>
       </c>
       <c r="V13" t="n">
         <v>1.3832</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4884</v>
+        <v>1.9667</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3205</v>
+        <v>1.8261</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1678</v>
+        <v>0.1406</v>
       </c>
       <c r="G14" t="n">
         <v>0.0829</v>
@@ -1546,13 +1546,13 @@
         <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0148</v>
+        <v>0.4932</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4704</v>
+        <v>0.0352</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4852</v>
+        <v>0.458</v>
       </c>
       <c r="V14" t="n">
         <v>0.6093</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8013</v>
+        <v>1.08</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2097</v>
+        <v>0.7063</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5916</v>
+        <v>0.3738</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6916</v>
+        <v>-0.119</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4623</v>
+        <v>0.2456</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2294</v>
+        <v>-0.3646</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2026</v>
+        <v>0.7798</v>
       </c>
       <c r="K15" t="n">
-        <v>0.431</v>
+        <v>0.7393</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4891</v>
+        <v>-0.8988</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8933</v>
+        <v>-0.4937</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4043</v>
+        <v>-0.4051</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6845</v>
+        <v>0.4079</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1899</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4946</v>
+        <v>0.4731</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2224</v>
+        <v>0.9865</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2224</v>
+        <v>1.1638</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1773</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4267</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0015</v>
+        <v>0.1086</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4282</v>
+        <v>0.5371</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.119</v>
+        <v>-0.6916</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2456</v>
+        <v>-0.4623</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3646</v>
+        <v>-0.2294</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7798</v>
+        <v>-0.2026</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7393</v>
+        <v>0.431</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8988</v>
+        <v>-0.4891</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4937</v>
+        <v>-0.8933</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4051</v>
+        <v>0.4043</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2454</v>
+        <v>0.5289</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.773</v>
+        <v>0.0888</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5276</v>
+        <v>0.4401</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9865</v>
+        <v>0.2224</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1638</v>
+        <v>0.2224</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1849</v>
+        <v>-0.2859</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5791</v>
+        <v>1.6802</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3942</v>
+        <v>-1.9661</v>
       </c>
       <c r="G17" t="n">
         <v>2.1409</v>
@@ -1780,13 +1780,13 @@
         <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7081</v>
+        <v>0.2373</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0108</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.719</v>
+        <v>0.147</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8828</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2727</v>
+        <v>-0.5797</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1992</v>
+        <v>2.0958</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4719</v>
+        <v>-2.6756</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1332</v>
+        <v>-0.4244</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5398</v>
+        <v>-0.2753</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5934</v>
+        <v>-0.149</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2158</v>
+        <v>1.5629</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1625</v>
+        <v>1.4415</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0533</v>
+        <v>0.1214</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9174</v>
+        <v>-1.9872</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3773</v>
+        <v>-1.7168</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5401</v>
+        <v>-0.2704</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3879</v>
+        <v>0.6899</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1145</v>
+        <v>0.4864</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2734</v>
+        <v>0.2035</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2772</v>
+        <v>-0.4545</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6732</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.55</v>
+        <v>-0.9116</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3412</v>
+        <v>0.7345</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8912</v>
+        <v>-1.6461</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8566</v>
@@ -1936,13 +1936,13 @@
         <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5019</v>
+        <v>0.1404</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.3454</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4502</v>
+        <v>-0.205</v>
       </c>
       <c r="V19" t="n">
         <v>1.2186</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6264</v>
+        <v>-1.0812</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9947</v>
+        <v>-0.8591</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6211</v>
+        <v>-0.2222</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4244</v>
+        <v>-0.7792</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2753</v>
+        <v>-1.2244</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.149</v>
+        <v>0.4451</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5629</v>
+        <v>0.0495</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4415</v>
+        <v>-0.5308</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1214</v>
+        <v>0.5803</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9872</v>
+        <v>-0.8287</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7168</v>
+        <v>-0.6935</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2704</v>
+        <v>-0.1352</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6432</v>
+        <v>0.284</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3853</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.258</v>
+        <v>0.2159</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4545</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6732</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1551</v>
+        <v>-1.1749</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.8119</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1949</v>
+        <v>-0.363</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7792</v>
+        <v>-2.1332</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2244</v>
+        <v>-1.5398</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4451</v>
+        <v>-0.5934</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0495</v>
+        <v>-0.2158</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5308</v>
+        <v>-0.1625</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5803</v>
+        <v>-0.0533</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8287</v>
+        <v>-1.9174</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6935</v>
+        <v>-1.3773</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1352</v>
+        <v>-0.5401</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2102</v>
+        <v>0.4856</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.033</v>
+        <v>0.1033</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2431</v>
+        <v>0.3823</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8849</v>
+        <v>-2.0949</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3318</v>
+        <v>-0.4329</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5531</v>
+        <v>-1.662</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0212</v>
@@ -2170,13 +2170,13 @@
         <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0251</v>
+        <v>0.8151</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6027</v>
+        <v>0.5016</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4224</v>
+        <v>0.3135</v>
       </c>
       <c r="V22" t="n">
         <v>1.6506</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6407</v>
+        <v>-2.4306</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7773</v>
+        <v>-1.6762</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3913</v>
@@ -2248,13 +2248,13 @@
         <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4996</v>
+        <v>-0.2896</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2283</v>
+        <v>-0.1272</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2713</v>
+        <v>-0.1624</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5545</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4021</v>
+        <v>-4.1454</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7587</v>
+        <v>-3.5564</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6434</v>
+        <v>-0.589</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9913</v>
@@ -2326,13 +2326,13 @@
         <v>0.3907</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4754</v>
+        <v>-0.2187</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3026</v>
+        <v>-0.1004</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1728</v>
+        <v>-0.1183</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1773</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4267</v>
+        <v>-5.0454</v>
       </c>
       <c r="E25" t="n">
         <v>-1.2236</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.2031</v>
+        <v>-3.8218</v>
       </c>
       <c r="G25" t="n">
         <v>0.7425</v>
@@ -2404,13 +2404,13 @@
         <v>1.3674</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.351</v>
+        <v>0.0303</v>
       </c>
       <c r="T25" t="n">
         <v>0.1432</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4942</v>
+        <v>-0.1129</v>
       </c>
       <c r="V25" t="n">
         <v>-3.2787</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.0573</v>
+        <v>-14.0572</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.4087</v>
+        <v>-1.408599999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.6487</v>
+        <v>-12.6488</v>
       </c>
       <c r="G26" t="n">
         <v>-9.4415</v>
@@ -2485,7 +2485,7 @@
         <v>3.6043</v>
       </c>
       <c r="T26" t="n">
-        <v>1.5696</v>
+        <v>1.5695</v>
       </c>
       <c r="U26" t="n">
         <v>2.0348</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484363_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484363_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1052</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.8279</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.2224</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,11 +1545,12 @@
       <c r="X13" t="n">
         <v>-5.431900000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9667</v>
+        <v>1.8349</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8261</v>
+        <v>1.8349</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1406</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0829</v>
+        <v>1.8349</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.065</v>
+        <v>1.2279</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1478</v>
+        <v>0.607</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1816</v>
+        <v>1.8349</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4937</v>
+        <v>1.2279</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6879</v>
+        <v>0.607</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0988</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5587</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5401</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4932</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0352</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.458</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.08</v>
+        <v>1.5279</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7063</v>
+        <v>1.5279</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3738</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.119</v>
+        <v>1.5279</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2456</v>
+        <v>0.921</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3646</v>
+        <v>0.607</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7798</v>
+        <v>1.5279</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7393</v>
+        <v>0.921</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8988</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4937</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4079</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4731</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9865</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6457000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1086</v>
+        <v>0.7063</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5371</v>
+        <v>0.3738</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6916</v>
+        <v>-0.119</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4623</v>
+        <v>0.2456</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2294</v>
+        <v>-0.3646</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2026</v>
+        <v>0.7798</v>
       </c>
       <c r="K16" t="n">
-        <v>0.431</v>
+        <v>0.7393</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4891</v>
+        <v>-0.8988</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8933</v>
+        <v>-0.4937</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4043</v>
+        <v>-0.4051</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5289</v>
+        <v>0.4079</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0888</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4401</v>
+        <v>0.4731</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2224</v>
+        <v>0.9865</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2224</v>
+        <v>1.1638</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1773</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2859</v>
+        <v>0.4388</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6802</v>
+        <v>0.2982</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9661</v>
+        <v>0.1406</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1409</v>
+        <v>-1.4451</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5859</v>
+        <v>-0.9859</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4449</v>
+        <v>-0.4591</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4029</v>
+        <v>-0.3463</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7682</v>
+        <v>-0.4272</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2619</v>
+        <v>-1.0988</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1824</v>
+        <v>-0.5587</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0795</v>
+        <v>-0.5401</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2373</v>
+        <v>0.4932</v>
       </c>
       <c r="T17" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0352</v>
       </c>
       <c r="U17" t="n">
-        <v>0.147</v>
+        <v>0.458</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8828</v>
+        <v>0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6642</v>
+        <v>0.6093</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5797</v>
+        <v>0.3387</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0958</v>
+        <v>-0.1984</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6756</v>
+        <v>0.5371</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4244</v>
+        <v>-0.9986</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2753</v>
+        <v>-0.7693</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.149</v>
+        <v>-0.2294</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5629</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4415</v>
+        <v>0.1241</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1214</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9872</v>
+        <v>-0.4891</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7168</v>
+        <v>-0.8933</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2704</v>
+        <v>0.4043</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6899</v>
+        <v>0.5289</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4864</v>
+        <v>0.0888</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2035</v>
+        <v>0.4401</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4545</v>
+        <v>0.2224</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0.2224</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6732</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9116</v>
+        <v>0.307</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7345</v>
+        <v>0.307</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6461</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8566</v>
+        <v>0.307</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1282</v>
+        <v>0.307</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7284</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1301</v>
+        <v>0.307</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7509</v>
+        <v>0.307</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6208</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7265</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3773</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3492</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1404</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3454</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.205</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0812</v>
+        <v>-0.5797</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8591</v>
+        <v>2.0958</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2222</v>
+        <v>-2.6756</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7792</v>
+        <v>-0.4244</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2244</v>
+        <v>-0.2753</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4451</v>
+        <v>-0.149</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0495</v>
+        <v>1.5629</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5308</v>
+        <v>1.4415</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5803</v>
+        <v>0.1214</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8287</v>
+        <v>-1.9872</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6935</v>
+        <v>-1.7168</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1352</v>
+        <v>-0.2704</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>0.284</v>
+        <v>0.6899</v>
       </c>
       <c r="T20" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.4864</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2159</v>
+        <v>0.2035</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.4545</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.6732</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1749</v>
+        <v>-0.9116</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8119</v>
+        <v>0.7345</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.363</v>
+        <v>-1.6461</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1332</v>
+        <v>-2.8566</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5398</v>
+        <v>-2.1282</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5934</v>
+        <v>-0.7284</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2158</v>
+        <v>-0.1301</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1625</v>
+        <v>-0.7509</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0533</v>
+        <v>0.6208</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9174</v>
+        <v>-2.7265</v>
       </c>
       <c r="N21" t="n">
         <v>-1.3773</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5401</v>
+        <v>-1.3492</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4856</v>
+        <v>0.1404</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1033</v>
+        <v>0.3454</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3823</v>
+        <v>-0.205</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0949</v>
+        <v>-1.0812</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4329</v>
+        <v>-0.8591</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.662</v>
+        <v>-0.2222</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0212</v>
+        <v>-0.7792</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1039</v>
+        <v>-1.2244</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9173</v>
+        <v>0.4451</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0039</v>
+        <v>0.0495</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7623</v>
+        <v>-0.5308</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2416</v>
+        <v>0.5803</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.0251</v>
+        <v>-0.8287</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8662</v>
+        <v>-0.6935</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.1589</v>
+        <v>-0.1352</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5395</v>
+        <v>-0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.1022</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8151</v>
+        <v>0.284</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5016</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3135</v>
+        <v>0.2159</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6506</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.4869</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4306</v>
+        <v>-1.1749</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6762</v>
+        <v>-0.8119</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.363</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3913</v>
+        <v>-2.1332</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0269</v>
+        <v>-1.5398</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3644</v>
+        <v>-0.5934</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5722</v>
+        <v>-0.2158</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6127</v>
+        <v>-0.1625</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0405</v>
+        <v>-0.0533</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.819</v>
+        <v>-1.9174</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4142</v>
+        <v>-1.3773</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4049</v>
+        <v>-0.5401</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2896</v>
+        <v>0.4856</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1272</v>
+        <v>0.1033</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1624</v>
+        <v>0.3823</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. PINEÑO JIMENEZ</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1454</v>
+        <v>-2.0949</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5564</v>
+        <v>-0.4329</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.589</v>
+        <v>-1.662</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9913</v>
+        <v>-2.0212</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5081</v>
+        <v>-1.1039</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4832</v>
+        <v>-0.9173</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3073</v>
+        <v>2.0039</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0409</v>
+        <v>0.7623</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3482</v>
+        <v>1.2416</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-4.0251</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.549</v>
+        <v>-1.8662</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.135</v>
+        <v>-2.1589</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.7581</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1488</v>
+        <v>-4.1022</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2187</v>
+        <v>0.8151</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1004</v>
+        <v>0.5016</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1183</v>
+        <v>0.3135</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1773</v>
+        <v>1.6506</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1773</v>
+        <v>0.4869</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. DI BONAVENTURA</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0454</v>
+        <v>-2.1209</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2236</v>
+        <v>-0.1547</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8218</v>
+        <v>-1.9661</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7425</v>
+        <v>0.306</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7836</v>
+        <v>1.3579</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0411</v>
+        <v>-1.0519</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2043</v>
+        <v>2.5679</v>
       </c>
       <c r="K25" t="n">
-        <v>2.4354</v>
+        <v>2.5403</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7688</v>
+        <v>0.0276</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.4617</v>
+        <v>-2.2619</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6518</v>
+        <v>-1.1824</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8099</v>
+        <v>-1.0795</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.5395</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.9069</v>
+        <v>-2.1488</v>
       </c>
       <c r="R25" t="n">
         <v>1.3674</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0303</v>
+        <v>0.2373</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1432</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1129</v>
+        <v>0.147</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.2787</v>
+        <v>-1.8828</v>
       </c>
       <c r="W25" t="n">
         <v>-0.6642</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.6146</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. BERMEJO JARAMILLO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,318 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.0572</v>
+        <v>-2.4306</v>
       </c>
       <c r="E26" t="n">
+        <v>-1.6762</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.7544999999999999</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.3913</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.0269</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.3644</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.5722</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.6127</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.819</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.4142</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.4049</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.2896</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.1272</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.1624</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>J. PINENO JIMENEZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4.1454</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-3.5564</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.589</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.9913</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.5081</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.4832</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.3073</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.3482</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.6840000000000001</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.549</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.135</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.2187</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.1004</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.1183</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.1773</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.1773</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>G. DI BONAVENTURA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-5.0454</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1.2236</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-3.8218</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.7425</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7836</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.0411</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.2043</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.4354</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.7688</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-2.4617</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1.6518</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.8099</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-2.5395</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.1129</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-3.2787</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-2.6146</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484363_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-14.0573</v>
+      </c>
+      <c r="E29" t="n">
         <v>-1.408599999999999</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F29" t="n">
         <v>-12.6488</v>
       </c>
-      <c r="G26" t="n">
-        <v>-9.4415</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="G29" t="n">
+        <v>-9.441600000000001</v>
+      </c>
+      <c r="H29" t="n">
         <v>-4.718799999999999</v>
       </c>
-      <c r="I26" t="n">
-        <v>-4.7228</v>
-      </c>
-      <c r="J26" t="n">
-        <v>10.7569</v>
-      </c>
-      <c r="K26" t="n">
-        <v>8.055399999999999</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="I29" t="n">
+        <v>-4.7227</v>
+      </c>
+      <c r="J29" t="n">
+        <v>10.7568</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8.0556</v>
+      </c>
+      <c r="L29" t="n">
         <v>2.7013</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M29" t="n">
         <v>-20.1982</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N29" t="n">
         <v>-12.7742</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O29" t="n">
         <v>-7.423999999999999</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P29" t="n">
         <v>-6.8371</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q29" t="n">
         <v>-18.5577</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R29" t="n">
         <v>11.7206</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S29" t="n">
         <v>3.6043</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T29" t="n">
         <v>1.5695</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U29" t="n">
         <v>2.0348</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V29" t="n">
         <v>-1.3832</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W29" t="n">
         <v>4.8226</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X29" t="n">
         <v>-6.2058</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
